--- a/drg/sansodhan of OK/analysis/excel for calculation/wall load calculation.xlsx
+++ b/drg/sansodhan of OK/analysis/excel for calculation/wall load calculation.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FBB725-53AE-40F5-BFA5-D72E43F2DE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61513AC6-6F6D-47CD-AC8D-F83D4BD6CCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interpoaltion" sheetId="1" r:id="rId1"/>
     <sheet name="wall load" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>y-y1=((y2-y1)/(x2-x1))*(x-x1)</t>
   </si>
@@ -92,6 +93,27 @@
   </si>
   <si>
     <t>meter</t>
+  </si>
+  <si>
+    <t>Steel size dia (mm)</t>
+  </si>
+  <si>
+    <t>Steel bar area (A)</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>8A</t>
+  </si>
+  <si>
+    <t>4-16mm + 4-20mm</t>
+  </si>
+  <si>
+    <t>For beam 6-12mm</t>
   </si>
 </sst>
 </file>
@@ -176,14 +198,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -191,11 +210,10 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -206,6 +224,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,7 +573,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -555,16 +582,16 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
       <c r="K1" s="3" t="s">
         <v>12</v>
       </c>
@@ -576,7 +603,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
+      <c r="A2" s="9"/>
       <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
@@ -589,14 +616,14 @@
       <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="12"/>
       <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
@@ -619,25 +646,25 @@
       <c r="C3" s="2">
         <v>0.23</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="2">
         <v>2.4891999999999999</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="2">
         <v>2.7178</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <f>C3*D3*B3</f>
         <v>10.992307200000001</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <f>C3*E3*B3</f>
         <v>12.0018048</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <f>0.7*F3</f>
         <v>7.6946150400000004</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <f>0.7*G3</f>
         <v>8.4012633599999997</v>
       </c>
@@ -660,25 +687,25 @@
       <c r="C4" s="2">
         <v>0.115</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="2">
         <v>2.4891999999999999</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="2">
         <v>2.7178</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <f>C4*D4*B4</f>
         <v>5.4961536000000004</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <f>C4*E4*B4</f>
         <v>6.0009024000000002</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <f t="shared" ref="H4" si="0">0.7*F4</f>
         <v>3.8473075200000002</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <f t="shared" ref="I4" si="1">0.7*G4</f>
         <v>4.2006316799999999</v>
       </c>
@@ -701,17 +728,17 @@
       <c r="C5" s="2">
         <v>0.115</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>0.91439999999999999</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="6">
+      <c r="E5" s="8"/>
+      <c r="F5" s="5">
         <f>C5*D5*B5</f>
         <v>2.0189952</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -726,4 +753,252 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C53DFB-C26A-4789-93E0-5F02EDBF3A4E}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <f>(A2*A2*PI())/4</f>
+        <v>50.26548245743669</v>
+      </c>
+      <c r="C2" s="2">
+        <f>2*B2</f>
+        <v>100.53096491487338</v>
+      </c>
+      <c r="D2" s="2">
+        <f>4*B2</f>
+        <v>201.06192982974676</v>
+      </c>
+      <c r="E2" s="2">
+        <f>8*B2</f>
+        <v>402.12385965949352</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" ref="B4:B12" si="0">(A4*A4*PI())/4</f>
+        <v>78.539816339744831</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C12" si="1">2*B4</f>
+        <v>157.07963267948966</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D12" si="2">4*B4</f>
+        <v>314.15926535897933</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E12" si="3">8*B4</f>
+        <v>628.31853071795865</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>113.09733552923255</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>226.1946710584651</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
+        <v>452.38934211693021</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="3"/>
+        <v>904.77868423386042</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="13">
+        <f>6*B6</f>
+        <v>678.58401317539528</v>
+      </c>
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="0"/>
+        <v>201.06192982974676</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>402.12385965949352</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>804.24771931898704</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="3"/>
+        <v>1608.4954386379741</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
+        <f>4*B8</f>
+        <v>804.24771931898704</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <f>D8+D10</f>
+        <v>2060.8847807549046</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="0"/>
+        <v>314.15926535897933</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
+        <v>628.31853071795865</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="2"/>
+        <v>1256.6370614359173</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="3"/>
+        <v>2513.2741228718346</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="0"/>
+        <v>490.87385212340519</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="1"/>
+        <v>981.74770424681037</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="2"/>
+        <v>1963.4954084936207</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="3"/>
+        <v>3926.9908169872415</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>